--- a/sample-data/KN02_locations.xlsx
+++ b/sample-data/KN02_locations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:D29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,6 +421,17 @@
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" t="str">
         <v>Location</v>
@@ -431,6 +442,9 @@
       <c r="C4" t="str">
         <v>Notes</v>
       </c>
+      <c r="D4" t="str">
+        <v>Spoken as</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -685,9 +699,37 @@
         <v/>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Tubbercurry</v>
+      </c>
+      <c r="B28" t="str">
+        <v>DA011</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Sligo border</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Dooleeg</v>
+      </c>
+      <c r="B29" t="str">
+        <v>DA014</v>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D29"/>
   </ignoredErrors>
 </worksheet>
 </file>